--- a/Result/profitability/7743.xlsx
+++ b/Result/profitability/7743.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM13"/>
+  <dimension ref="A1:AM14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2083,6 +2083,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>7743</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>211</v>
+      </c>
+      <c r="D14" t="n">
+        <v>145</v>
+      </c>
+      <c r="E14" t="n">
+        <v>66</v>
+      </c>
+      <c r="F14" t="n">
+        <v>31.37</v>
+      </c>
+      <c r="G14" t="n">
+        <v>25</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>11.82%</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>26</v>
+      </c>
+      <c r="K14" t="n">
+        <v>21</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>29.905</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.5199999999999999</v>
+      </c>
+      <c r="X14" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8.790000000000003</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.3892825509300266</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.6599999999999999</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-7.333333333333333</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.05540499849442937</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK14" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
